--- a/output_data/DC_Park_OG_Auto.xlsx
+++ b/output_data/DC_Park_OG_Auto.xlsx
@@ -437,122 +437,122 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>25.2091678731138</v>
+        <v>25.49510538439408</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20.01224600560987</v>
+        <v>19.855081095655</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>13.31336610137357</v>
+        <v>13.39829979712372</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>14.689157562994</v>
+        <v>14.34389415105479</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17.52627060447989</v>
+        <v>17.7462316697987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18.56877237101585</v>
+        <v>18.82524096349625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>32.87521772861606</v>
+        <v>32.97051340486168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67.69687771732146</v>
+        <v>67.88697704630788</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>92.64298619758006</v>
+        <v>92.96695932865435</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116.9927780426974</v>
+        <v>118.6165220729491</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111.7729464260848</v>
+        <v>110.6647995912559</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109.8297362488854</v>
+        <v>106.8606696171997</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105.1737548020003</v>
+        <v>106.2553514552125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110.6626196013626</v>
+        <v>110.115408012574</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109.8931204771532</v>
+        <v>109.51871119451</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101.7574119535379</v>
+        <v>103.5730164258574</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96.27026087914382</v>
+        <v>94.7884667284153</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89.14062508854016</v>
+        <v>90.68386883261037</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>82.90295685091678</v>
+        <v>84.40327154539246</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>77.41912560075809</v>
+        <v>76.16712808801691</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>65.57541925535151</v>
+        <v>65.55554370862515</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>56.16700384346643</v>
+        <v>58.42358214393695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>46.79141845884793</v>
+        <v>47.6175753141871</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>39.54433289142256</v>
+        <v>40.53689953687272</v>
       </c>
     </row>
   </sheetData>
